--- a/Tables/G_FXInfoTable.xlsx
+++ b/Tables/G_FXInfoTable.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Common" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="README" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Common" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -99,6 +100,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -302,6 +307,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <sheetData/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="22" width="12.63"/>
   </cols>

--- a/Tables/G_FXInfoTable.xlsx
+++ b/Tables/G_FXInfoTable.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Description</t>
   </si>
@@ -30,6 +30,9 @@
   </si>
   <si>
     <t>FXResKinds</t>
+  </si>
+  <si>
+    <t>Delay</t>
   </si>
   <si>
     <t>효과 샘플</t>
@@ -341,7 +344,9 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3"/>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -362,7 +367,7 @@
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="5">
         <v>0.0</v>
@@ -379,7 +384,9 @@
       <c r="F2" s="3">
         <v>-1.0</v>
       </c>
-      <c r="G2" s="3"/>
+      <c r="G2" s="3">
+        <v>0.0</v>
+      </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>

--- a/Tables/G_FXInfoTable.xlsx
+++ b/Tables/G_FXInfoTable.xlsx
@@ -371,7 +371,17 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="24" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="10.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="7.25"/>
+    <col customWidth="1" min="6" max="7" width="10.75"/>
+    <col customWidth="1" min="8" max="8" width="10.88"/>
+    <col customWidth="1" min="9" max="9" width="5.25"/>
+    <col customWidth="1" min="10" max="10" width="8.5"/>
+    <col customWidth="1" min="11" max="11" width="7.25"/>
+    <col customWidth="1" min="12" max="28" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12046,7 +12056,17 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="24" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="10.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="9.38"/>
+    <col customWidth="1" min="6" max="7" width="10.75"/>
+    <col customWidth="1" min="8" max="8" width="10.88"/>
+    <col customWidth="1" min="9" max="9" width="5.25"/>
+    <col customWidth="1" min="10" max="10" width="8.5"/>
+    <col customWidth="1" min="11" max="11" width="7.25"/>
+    <col customWidth="1" min="12" max="28" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23721,7 +23741,17 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="24" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="12.0"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="9.38"/>
+    <col customWidth="1" min="6" max="7" width="10.75"/>
+    <col customWidth="1" min="8" max="8" width="10.88"/>
+    <col customWidth="1" min="9" max="9" width="5.25"/>
+    <col customWidth="1" min="10" max="10" width="8.5"/>
+    <col customWidth="1" min="11" max="11" width="7.25"/>
+    <col customWidth="1" min="12" max="28" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/Tables/G_FXInfoTable.xlsx
+++ b/Tables/G_FXInfoTable.xlsx
@@ -28607,15 +28607,15 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="11">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6))</f>
         <v>0</v>
       </c>
       <c r="K2" s="11">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1)</f>
         <v>-1</v>
       </c>
       <c r="L2" s="11">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1)</f>
         <v>1</v>
       </c>
       <c r="M2" s="4">
@@ -45320,15 +45320,15 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="11">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6))</f>
         <v>100000000</v>
       </c>
       <c r="K2" s="11">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1)</f>
         <v>99999999</v>
       </c>
       <c r="L2" s="11">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1)</f>
         <v>100000001</v>
       </c>
       <c r="M2" s="4">
@@ -62033,15 +62033,15 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="11">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6))</f>
         <v>200000000</v>
       </c>
       <c r="K2" s="11">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1)</f>
         <v>199999999</v>
       </c>
       <c r="L2" s="11">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1)</f>
         <v>200000001</v>
       </c>
       <c r="M2" s="4">
